--- a/DataRepo/tests/data/full_tiny_study/study.xlsx
+++ b/DataRepo/tests/data/full_tiny_study/study.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-LOCAL/TRACEBASE/tracebase/DataRepo/data/tests/full_tiny_study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/full_tiny_study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E61D14-2B0F-7844-B726-7F206D922084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F67070-D7D3-3F4D-8AB3-10668E5ECDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5600" yWindow="7700" windowWidth="38360" windowHeight="13720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5600" yWindow="7700" windowWidth="38360" windowHeight="13720" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="5" r:id="rId1"/>
@@ -578,10 +578,10 @@
     <t>skip</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/full_tiny_study/alafasted/alafasted_cor.xlsx</t>
-  </si>
-  <si>
-    <t>DataRepo/data/tests/full_tiny_study/glnfasted/glnfasted1_cor.xlsx</t>
+    <t>DataRepo/tests/data/full_tiny_study/glnfasted/glnfasted1_cor.xlsx</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/full_tiny_study/alafasted/alafasted_cor.xlsx</t>
   </si>
 </sst>
 </file>
@@ -12581,8 +12581,8 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>177</v>
+      <c r="A2" s="15" t="s">
+        <v>176</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>121</v>
@@ -12593,7 +12593,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>121</v>
